--- a/SQExcel.Portal/src/content/docs/ja/docs/images/input-sheet-overview/input-sheet-overview.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/input-sheet-overview/input-sheet-overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\input-sheet-overview\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\input-sheet-overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9255CFAD-FE78-4499-A4E2-3A4C6B6C80A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFD9834-3CF0-42DC-B4FB-50CFA4EDEC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4350" yWindow="2890" windowWidth="18680" windowHeight="11900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1590" yWindow="90" windowWidth="19420" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT_SHEET_OVERVIEW" sheetId="3" r:id="rId1"/>
@@ -608,22 +608,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>14941</xdr:rowOff>
+      <xdr:colOff>7471</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>7471</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228601</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>123629</xdr:rowOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>4483</xdr:colOff>
+      <xdr:row>169</xdr:row>
+      <xdr:rowOff>68820</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="18" name="グループ化 17">
+        <xdr:cNvPr id="29" name="グループ化 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0C6BE65-DAF3-994A-BBEB-96BE5F658641}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C16EE71-814F-0E7C-8318-E1950A89D6B2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -631,18 +631,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="471715" y="1602441"/>
-          <a:ext cx="10842172" cy="6458688"/>
-          <a:chOff x="477372" y="1600200"/>
-          <a:chExt cx="10804712" cy="6509488"/>
+          <a:off x="470647" y="33819353"/>
+          <a:ext cx="10650071" cy="5387879"/>
+          <a:chOff x="477371" y="33383071"/>
+          <a:chExt cx="10804712" cy="5319149"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="3" name="図 2">
+          <xdr:cNvPr id="28" name="図 27">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55AACC83-6264-44FA-9791-4F47CEFE9F45}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC233BE1-67AA-4539-AE3C-2DFD297DA471}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -658,8 +658,8 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="477372" y="1600200"/>
-            <a:ext cx="10804712" cy="6509488"/>
+            <a:off x="477371" y="33383071"/>
+            <a:ext cx="10804712" cy="5319149"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -668,10 +668,10 @@
       </xdr:pic>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <xdr:cNvPr id="10" name="正方形/長方形 9">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24F61E51-6146-4A15-9081-E9E9EA6C0AB5}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E18A4B7-8272-4747-AE61-93FFB07E4406}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -679,8 +679,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="8799629" y="2472291"/>
-            <a:ext cx="2393674" cy="1371938"/>
+            <a:off x="1335961" y="38220565"/>
+            <a:ext cx="4474347" cy="311235"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -727,66 +727,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>7470</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>149413</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>190350</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>166370</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E11929B9-0F57-FC9F-D1F5-6D587961790A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="470646" y="9876119"/>
-          <a:ext cx="8520057" cy="5343486"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>146</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>14941</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>169</xdr:row>
-      <xdr:rowOff>134970</xdr:rowOff>
+      <xdr:colOff>228601</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123629</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="11" name="グループ化 10">
+        <xdr:cNvPr id="5" name="グループ化 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E658E2BC-7D9E-7E24-892D-547AA077882C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54DE49A9-D6BF-144E-828A-1EAA54F201F9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -794,18 +750,122 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="471714" y="33110714"/>
-          <a:ext cx="10842172" cy="5351042"/>
-          <a:chOff x="469900" y="33375600"/>
-          <a:chExt cx="10801350" cy="5392770"/>
+          <a:off x="463177" y="1636059"/>
+          <a:ext cx="10650071" cy="6593158"/>
+          <a:chOff x="469901" y="1615141"/>
+          <a:chExt cx="10801350" cy="6509488"/>
         </a:xfrm>
       </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="18" name="グループ化 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0C6BE65-DAF3-994A-BBEB-96BE5F658641}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="469901" y="1615141"/>
+            <a:ext cx="10801350" cy="6509488"/>
+            <a:chOff x="477372" y="1600200"/>
+            <a:chExt cx="10804712" cy="6509488"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="3" name="図 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55AACC83-6264-44FA-9791-4F47CEFE9F45}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="477372" y="1600200"/>
+              <a:ext cx="10804712" cy="6509488"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="正方形/長方形 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24F61E51-6146-4A15-9081-E9E9EA6C0AB5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8799629" y="2472291"/>
+              <a:ext cx="2393674" cy="1371938"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="9" name="図 8">
+          <xdr:cNvPr id="2" name="図 1">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE4C983E-A649-6C1C-FBB9-2C036B5E9079}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95BCEEAE-87D2-482B-AF05-FC5ED1ECAE1A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -821,69 +881,107 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="469900" y="33375600"/>
-            <a:ext cx="10801350" cy="5392770"/>
+            <a:off x="492312" y="1637552"/>
+            <a:ext cx="252070" cy="225939"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="10" name="正方形/長方形 9">
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>7470</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>149413</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>190350</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>166370</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="19" name="グループ化 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75BAE6F0-CCE2-069E-ED44-29070F76A062}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="470646" y="9876119"/>
+          <a:ext cx="8520057" cy="5343486"/>
+          <a:chOff x="477370" y="9750613"/>
+          <a:chExt cx="8641080" cy="5274757"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="6" name="図 5">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E18A4B7-8272-4747-AE61-93FFB07E4406}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E11929B9-0F57-FC9F-D1F5-6D587961790A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1338035" y="38221557"/>
-            <a:ext cx="4473123" cy="375717"/>
+            <a:off x="477370" y="9750613"/>
+            <a:ext cx="8641080" cy="5274757"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
         </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="17" name="図 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA0E3B62-22FA-485A-80BF-03F248CDC90E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="522194" y="9787964"/>
+            <a:ext cx="252070" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -902,10 +1000,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="15" name="グループ化 14">
+        <xdr:cNvPr id="22" name="グループ化 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23AD3569-49C2-2ADA-9A5C-7E20DD33A238}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C1EC69E-2386-F41F-DE74-877F88251F26}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -913,18 +1011,232 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="453571" y="16637001"/>
-          <a:ext cx="8673737" cy="8017492"/>
+          <a:off x="449302" y="16987585"/>
+          <a:ext cx="8515788" cy="8185580"/>
           <a:chOff x="452664" y="16769444"/>
           <a:chExt cx="8640173" cy="8080992"/>
         </a:xfrm>
       </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="15" name="グループ化 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23AD3569-49C2-2ADA-9A5C-7E20DD33A238}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="452664" y="16769444"/>
+            <a:ext cx="8640173" cy="8080992"/>
+            <a:chOff x="452664" y="16769444"/>
+            <a:chExt cx="8640173" cy="8080992"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="7" name="図 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3260AE0A-6183-5244-EA11-924220C80C66}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="452664" y="16769444"/>
+              <a:ext cx="8640173" cy="8070879"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="12" name="正方形/長方形 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC4BC6A1-99D7-4119-B047-075F757256B5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="596900" y="17994085"/>
+              <a:ext cx="6994071" cy="713015"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13" name="正方形/長方形 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFB60C93-1CE8-4D0F-A87D-9757554A58CE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="633186" y="19191516"/>
+              <a:ext cx="6975928" cy="531585"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="14" name="正方形/長方形 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F68153E-A905-4E9B-827E-ED6A18B8DC34}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6108700" y="24440243"/>
+              <a:ext cx="1427842" cy="410193"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="7" name="図 6">
+          <xdr:cNvPr id="21" name="図 20">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3260AE0A-6183-5244-EA11-924220C80C66}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E63BF5DF-73CF-4753-B3E3-473F2845C0B2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -933,208 +1245,43 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="452664" y="16769444"/>
-            <a:ext cx="8640173" cy="8070879"/>
+            <a:off x="529665" y="16822270"/>
+            <a:ext cx="252070" cy="225939"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="正方形/長方形 11">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC4BC6A1-99D7-4119-B047-075F757256B5}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="596900" y="17994085"/>
-            <a:ext cx="6994071" cy="713015"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="13" name="正方形/長方形 12">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFB60C93-1CE8-4D0F-A87D-9757554A58CE}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="633186" y="19191516"/>
-            <a:ext cx="6975928" cy="531585"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="14" name="正方形/長方形 13">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F68153E-A905-4E9B-827E-ED6A18B8DC34}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6108700" y="24440243"/>
-            <a:ext cx="1427842" cy="410193"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>18143</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>112</xdr:row>
       <xdr:rowOff>18144</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>48</xdr:col>
-      <xdr:colOff>10886</xdr:colOff>
+      <xdr:colOff>10888</xdr:colOff>
       <xdr:row>141</xdr:row>
       <xdr:rowOff>125768</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="27" name="グループ化 26">
+        <xdr:cNvPr id="24" name="グループ化 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFD9EB03-19C3-1C4F-C934-C9A1DB8E4BBE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B11C83E-B026-78F4-CE35-A89D0E45585A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1142,18 +1289,151 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="489857" y="25418144"/>
-          <a:ext cx="10842172" cy="6684410"/>
-          <a:chOff x="488043" y="25621344"/>
-          <a:chExt cx="10800443" cy="6737024"/>
+          <a:off x="463177" y="25956026"/>
+          <a:ext cx="10663946" cy="6823683"/>
+          <a:chOff x="469683" y="25621344"/>
+          <a:chExt cx="10818803" cy="6737024"/>
         </a:xfrm>
       </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="27" name="グループ化 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFD9EB03-19C3-1C4F-C934-C9A1DB8E4BBE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="488043" y="25621344"/>
+            <a:ext cx="10800443" cy="6737024"/>
+            <a:chOff x="488043" y="25621344"/>
+            <a:chExt cx="10800443" cy="6737024"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="8" name="図 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4F86D96-00D6-A87E-F13A-ADC2F6B0AF9F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="488043" y="25621344"/>
+              <a:ext cx="10800443" cy="6737024"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="正方形/長方形 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC2D81E0-1D64-4C8B-829D-2B91BDBB29BE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6010520" y="29857236"/>
+              <a:ext cx="814608" cy="363553"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="26" name="図 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33F98A7F-213D-BD53-0B10-A61582B17E28}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7683126" y="26736629"/>
+              <a:ext cx="1097518" cy="1428002"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="8" name="図 7">
+          <xdr:cNvPr id="23" name="図 22">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4F86D96-00D6-A87E-F13A-ADC2F6B0AF9F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0930F556-2058-478D-B433-B4EEAF2ED444}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1162,99 +1442,15 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="488043" y="25621344"/>
-            <a:ext cx="10800443" cy="6737024"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="16" name="正方形/長方形 15">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC2D81E0-1D64-4C8B-829D-2B91BDBB29BE}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="6010520" y="29857236"/>
-            <a:ext cx="814608" cy="363553"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="26" name="図 25">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33F98A7F-213D-BD53-0B10-A61582B17E28}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7683126" y="26736629"/>
-            <a:ext cx="1097518" cy="1428002"/>
+            <a:off x="469683" y="25648212"/>
+            <a:ext cx="252070" cy="225938"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
